--- a/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B31AF458-DB0F-4ACC-9109-EE4E14800431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DDF13B-04FD-4D95-913D-D801974BA7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DDF13B-04FD-4D95-913D-D801974BA7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A0537DB-552F-4E49-904F-70C48CA613F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A0537DB-552F-4E49-904F-70C48CA613F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E322C8E2-B62E-402D-8CDE-668750A39552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_TJK_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E322C8E2-B62E-402D-8CDE-668750A39552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B8E525B-F9A6-45E6-86B2-A972C89E3C2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
